--- a/news_daily/2026-09-25.xlsx
+++ b/news_daily/2026-09-25.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,10 +92,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -991,6 +1015,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1026,28 +1054,32 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1087,7 +1119,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1096,7 +1128,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>1651da77f9b44a84b3f3a2b440ef7dba</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>34d31cedf47c3cb9e0dee062</t>
@@ -1117,7 +1153,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1161,6 +1201,22 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1196,28 +1252,32 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1257,7 +1317,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1266,7 +1326,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>68d2b620a2214a9ebc0ac02a304288d0</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>a444032cdf64b0b2926c1d94</t>
@@ -1287,7 +1351,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1331,176 +1399,220 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Apple (AAPL) Reaches $250 Million Siri Settlement Over Recent iPhone Claims</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeUdJUVJKX1J6R2k4dkJUcGNJcGZQWjd2MmpRSGlBeEJ6U3NtUXJyOVotTTZkbllBNVM5TWFLeFlhNGFWUzJaS1M2N3lFY1JkMUtRa0NkWm9YWWlybHB2Umt1dHA3ZnJBNXllR3drUEc4cGMwUXZfR0c2YVd4NklfTDB5ZlJNTk5LdVc5NGc2NGJJa2w4UmFfQVNFaw?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>a783c61dc5174cb0ab4281996cf01a0c</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>0bf509d54bcdb39afb60964e</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>cd6a897f55232c7d82807601</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeUdJUVJKX1J6R2k4dkJUcGNJcGZQWjd2MmpRSGlBeEJ6U3NtUXJyOVotTTZkbllBNVM5TWFLeFlhNGFWUzJaS1M2N3lFY1JkMUtRa0NkWm9YWWlybHB2Umt1dHA3ZnJBNXllR3drUEc4cGMwUXZfR0c2YVd4NklfTDB5ZlJNTk5LdVc5NGc2NGJJa2w4UmFfQVNFaw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>0bf509d54bcdb39afb60964e</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>cd6a897f55232c7d82807601</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1536,28 +1648,32 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1597,7 +1713,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1606,7 +1722,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>cdeba72f020a427da012c4dc953ef928</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>476d18e83d8c100b4cfba55b</t>
@@ -1627,7 +1747,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1671,168 +1795,188 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Goldman Sachs</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Goldman Sachs Warns on Big Tech AI Debt Flood</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>'-0.902</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNY0ZscDJiblByaHZ4YmU5a1ZZZXBlUXlORER0TXp2N3Z5TGU4dThTSUZpdlFHS1FUMkVjSjYybFdJS0VROHlDOWR2Q05VbEJfUjJTemxBdFVUT25OQVhacXF2ak1mbFZFZWZrSmdfckhmeHV5WlJGRjBnTFBfLURjamQtb2JxMUFILWM2elF1ZEtFQUJ2UmEw?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>flood</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>ac7a8f90c724cebdda7c0d31</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t>806fae1a4aecc4bbed0b8551</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr"/>
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1868,28 +2012,32 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1929,7 +2077,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -1938,7 +2086,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>33da3a7628504741afcd95e70d26aa4d</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>465ec24f6e455d30c73f1f14</t>
@@ -1959,7 +2111,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -2003,6 +2159,22 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2173,168 +2345,176 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Costco</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Costco uses US$184 million in tariff refunds to lower prices</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>0.506</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPOXhReWdQa3dpN3ZLMjhMY2lEbUVCM3hwTllubl96d1BQVnVIZDF5eUt6Y1ZCcFpIT1dwdUlMTGw1Q01GdXpvQ09ibzFTOUMtRFRYazFjX2FsNmc3elFjb2xNVjlIVnpRc0JTY3lqMHZUZVFzeFBEOHgyeG5lR0drYQ?oc=5</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="V10" s="3" t="inlineStr">
         <is>
           <t>Yahoo! Finance Canada</t>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>5cf5494211d8ed3c0e855a07</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AD10" s="3" t="inlineStr">
         <is>
           <t>378a75d74f8c41a16823f329</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2505,6 +2685,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2675,171 +2859,179 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Costco</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Costco CFO doubles down on tariff strategy, winks at churro comeback</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>關稅</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>'-0.489</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOOUpOUUhVUmhsaS1YcE1JWWVoaEVpSUQwU0I3cGUyY2JGZHl4VVJjZEN2QWF5X19BTUZPUl9EUW9KempmMkZKc041ZUE4bjlJRHg0SEpBZTBVUHJTZGFhOW84SXA4aVViT181cUlPM2ZWbFdoNld3Umdual96Sm80NjZDVWlraW54TF9NZjEtRFpzamZHa3U2VUd2RmVVaW8?oc=5</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>CFO Dive</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t>GEOPOLITICAL</t>
         </is>
       </c>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>TARIFF</t>
         </is>
       </c>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>tariff</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>14c244ee28438798ebc7d4c4</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AD13" s="3" t="inlineStr">
         <is>
           <t>b9917d119333066eabbfed44</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AX13" s="3" t="inlineStr"/>
+      <c r="AY13" s="3" t="inlineStr"/>
+      <c r="AZ13" s="3" t="inlineStr"/>
+      <c r="BA13" s="3" t="inlineStr"/>
+      <c r="BB13" s="3" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="BC13" s="4" t="inlineStr">
+      <c r="BC13" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
+      <c r="BD13" s="3" t="inlineStr"/>
+      <c r="BE13" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr">
+      <c r="BF13" s="3" t="inlineStr"/>
+      <c r="BG13" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2850,7 +3042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2913,6 +3105,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3214,6 +3410,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -3378,1369 +3594,733 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Mastercard Stock Holds Flat as $25 Billion Stablecoin Settlement Goes Live</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Apple (AAPL) Reaches $250 Million Siri Settlement Over Recent iPhone Claims</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeUdJUVJKX1J6R2k4dkJUcGNJcGZQWjd2MmpRSGlBeEJ6U3NtUXJyOVotTTZkbllBNVM5TWFLeFlhNGFWUzJaS1M2N3lFY1JkMUtRa0NkWm9YWWlybHB2Umt1dHA3ZnJBNXllR3drUEc4cGMwUXZfR0c2YVd4NklfTDB5ZlJNTk5LdVc5NGc2NGJJa2w4UmFfQVNFaw?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>a783c61dc5174cb0ab4281996cf01a0c</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>0bf509d54bcdb39afb60964e</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>cd6a897f55232c7d82807601</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.936</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWMtZHJnNWppaUpjZTJWeDZ5QVZ1VFR4QzVQb0pZaE4xNTdaVGpWREVxV3pLNWNoQkp3Sk1uYVQyS3loYmdGdVp1OUt5aFpXZ3k5amJDQkc2TEdDNE4xZDdCTExtTXk4Vk9YRWo5RXBrZlczdDhXcjJhaEhWdzd0QkhQbHh2SlZWTTc1SXk0QTBLODAyOXA5S2NCZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>34d31cedf47c3cb9e0dee062</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>dc6c2a8526e8fde0de019f7a</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CVS texted consumers after they opted out, a new class action lawsuit claims.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum (MPC) Could Be 20% Overvalued Following Diesel Export Ban Review</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>'-0.806</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNX1A4SzFfMEZfODdMZ3dMRlB6bEdQRHZma3M2QWY1TXpUdldxTjRnR1MzV2hDMTh6aUxRNUYxT3hUVE11bEhwbjNLZFlnT0RKb0lPV21sdDdqdVNoNHBmaTBkNlJvUU9fN005d0UwQ2NLMVdFTTd1MVhjM1p6Q252TXZEa29yeUp6LWhxbFF4YVMxX1o2b3JGelo1akF1ZklwUG9zTjM1azk5OFJ5bmFoR0pkRFFTYmZsMGlqMw?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>a444032cdf64b0b2926c1d94</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>8630ba2dd82ff84adddaa7f4</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcklWUHk3Nm44SEEtcE1NZFlEa1pFXzZlajhLdXExLUpLcUxDeGRsM3FoeXN2VDB4dkpMNk9laUkybUFSRVM0WnhQa3ItWG1aTXg5OGVReFFKSWo2V2Q4M0ExRmlqY2hUTEo0UjQtQVlXMDNLVGtuMWZicFFXVUNTeVdHOVJNTk1jV19sN0VMcmFibXIydzdvak5TQ2g?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>export ban</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>bdbc7addd11317b5a78aec33</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>013747d7355deb6f85ac13a8</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr"/>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="BC4" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BG4" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Apple (AAPL) Reaches $250 Million Siri Settlement Over Recent iPhone Claims</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum (MPC) Faces Fresh Uncertainty After Trump Backs Diesel Export Ban</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>'-0.923</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeUdJUVJKX1J6R2k4dkJUcGNJcGZQWjd2MmpRSGlBeEJ6U3NtUXJyOVotTTZkbllBNVM5TWFLeFlhNGFWUzJaS1M2N3lFY1JkMUtRa0NkWm9YWWlybHB2Umt1dHA3ZnJBNXllR3drUEc4cGMwUXZfR0c2YVd4NklfTDB5ZlJNTk5LdVc5NGc2NGJJa2w4UmFfQVNFaw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObmk3aklBSlZNWXFaTlhDNFFFXzI1RDVSb2hHbHpQWi1SOE1sMjctSzVZSTQ4b1hXR0pBLWVNTm5LZFExTWxZYXhGaW1pOEFvQlhzR3ZtVENyeVlVU1A5d2JPQndxSTdEZ2UzZTdUeW1VdFpSNkI4VVROWWs3a1JvUE9uYUlPUlk2X0ZGd3pPUi1Ma3pMeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>0bf509d54bcdb39afb60964e</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>cd6a897f55232c7d82807601</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>export ban</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>dc063b21e36a663b69ad8c44</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>7af0ec7ca161a30427a2941f</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DRI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Darden Restaurants, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Do you qualify for a payment from the $30 million Equifax class action settlement?</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>DRI Q3 Deep Dive: Margin Pressures and Consumer Trends Shape Restaurant Performance</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>'-0.935</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBkQmFZNnBXYmg0NGN2STNJZklhOWtvNGFWUU8yeXIxRGhjSkZHMktKdDY1eDI1N0ppX2V0Z25JLWNxeTdBZmZDZC01NF9qY211X3pqejE1NWdtMkFoUVlKVnAyVFotT2N5WEs3UXpXNmlQQ0NRUHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Claim Depot</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>476d18e83d8c100b4cfba55b</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>b2c836d8fc10acc99e4b0b56</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdmhZLVF0MThrUng3ZVdlSUU3Zk8yMERjTDF5N3h3cXREQ1p6UHdRNlpoWm0tRWFLdFhud2dFMW15dEgwYVN0aTNzQjNsZUZKR2pUT3pGczBMWHA0WERvQnh4X0Z6UGZaV1huSFpJTUdUYUdINmtPNEt5N0VKZ19qVjFUVG9CSjI2YThMMkptcWluQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>488c2fb90c1b2e6f9e17a0c6</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>a6b18f2660b88eee008a8a12</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
+        <is>
+          <t>DRI</t>
+        </is>
+      </c>
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-25T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Mastercard (MA) Rolls Out SoFiUSD Settlement, Is The 24% Undervalued View Still Compelling?</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.508</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZk1RNUlUTGd0Y3I3NGkzcmh0eUo2cUI5bnlfSTJsLUZuMjl1YW1IcGEtRHRVV2h6QzBDYnl3X0wtWFN0MGtOTFM0RktlcHVIYW8yaXp6cUtvNkdsMG5RWm4yVTdLUDRLanJKNG83UTlNam1ESG54TVZRMHpab0pMVG5UVUhjclJSSzNlR0pucFZzQ0Y1WGY0ZHdzVUtwaWIwTndlSER3?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>465ec24f6e455d30c73f1f14</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>ffcf01f6d64f93687045b49d</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum (MPC) Could Be 20% Overvalued Following Diesel Export Ban Review</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>出口管制</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcklWUHk3Nm44SEEtcE1NZFlEa1pFXzZlajhLdXExLUpLcUxDeGRsM3FoeXN2VDB4dkpMNk9laUkybUFSRVM0WnhQa3ItWG1aTXg5OGVReFFKSWo2V2Q4M0ExRmlqY2hUTEo0UjQtQVlXMDNLVGtuMWZicFFXVUNTeVdHOVJNTk1jV19sN0VMcmFibXIydzdvak5TQ2g?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>EXPORT_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>export ban</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>bdbc7addd11317b5a78aec33</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>013747d7355deb6f85ac13a8</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr"/>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum (MPC) Faces Fresh Uncertainty After Trump Backs Diesel Export Ban</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>出口管制</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxObmk3aklBSlZNWXFaTlhDNFFFXzI1RDVSb2hHbHpQWi1SOE1sMjctSzVZSTQ4b1hXR0pBLWVNTm5LZFExTWxZYXhGaW1pOEFvQlhzR3ZtVENyeVlVU1A5d2JPQndxSTdEZ2UzZTdUeW1VdFpSNkI4VVROWWs3a1JvUE9uYUlPUlk2X0ZGd3pPUi1Ma3pMeEE?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>EXPORT_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>export ban</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>dc063b21e36a663b69ad8c44</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>7af0ec7ca161a30427a2941f</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="2" t="inlineStr"/>
-      <c r="BE9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Darden Restaurants, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>DRI Q3 Deep Dive: Margin Pressures and Consumer Trends Shape Restaurant Performance</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.935</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdmhZLVF0MThrUng3ZVdlSUU3Zk8yMERjTDF5N3h3cXREQ1p6UHdRNlpoWm0tRWFLdFhud2dFMW15dEgwYVN0aTNzQjNsZUZKR2pUT3pGczBMWHA0WERvQnh4X0Z6UGZaV1huSFpJTUdUYUdINmtPNEt5N0VKZ19qVjFUVG9CSjI2YThMMkptcWluQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>488c2fb90c1b2e6f9e17a0c6</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>a6b18f2660b88eee008a8a12</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4751,7 +4331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4814,6 +4394,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5117,9 +4701,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5130,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5193,6 +4797,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5496,9 +5104,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5509,7 +5137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5559,477 +5187,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="n">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="4" t="n">
+      <c r="V8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
+      <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-25.xlsx
+++ b/news_daily/2026-09-25.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f4f6d76f5b6446f58e46358acf0feae7</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>8bc9982dd4bcabf20077b66c</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1017,8 +1029,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2225,13 +2245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2280,7 +2304,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>cd9c53d5115c4c88a06a89280bfe5985</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>bdbc7addd11317b5a78aec33</t>
@@ -2301,7 +2329,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2347,8 +2379,16 @@
       <c r="BH9" s="2" t="inlineStr"/>
       <c r="BI9" s="2" t="inlineStr"/>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2565,13 +2605,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2620,7 +2664,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>682734557f1646e793237149954e377d</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>dc063b21e36a663b69ad8c44</t>
@@ -2641,7 +2689,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2687,182 +2739,214 @@
       <c r="BH11" s="2" t="inlineStr"/>
       <c r="BI11" s="2" t="inlineStr"/>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>DRI</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Darden Restaurants, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>2026-09-25T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>DRI Q3 Deep Dive: Margin Pressures and Consumer Trends Shape Restaurant Performance</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>'-0.935</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdmhZLVF0MThrUng3ZVdlSUU3Zk8yMERjTDF5N3h3cXREQ1p6UHdRNlpoWm0tRWFLdFhud2dFMW15dEgwYVN0aTNzQjNsZUZKR2pUT3pGczBMWHA0WERvQnh4X0Z6UGZaV1huSFpJTUdUYUdINmtPNEt5N0VKZ19qVjFUVG9CSjI2YThMMkptcWluQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>a41f9c2c6ee644d6824545b190e20863</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>488c2fb90c1b2e6f9e17a0c6</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>a6b18f2660b88eee008a8a12</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>'-0.935</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdmhZLVF0MThrUng3ZVdlSUU3Zk8yMERjTDF5N3h3cXREQ1p6UHdRNlpoWm0tRWFLdFhud2dFMW15dEgwYVN0aTNzQjNsZUZKR2pUT3pGczBMWHA0WERvQnh4X0Z6UGZaV1huSFpJTUdUYUdINmtPNEt5N0VKZ19qVjFUVG9CSjI2YThMMkptcWluQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>488c2fb90c1b2e6f9e17a0c6</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>a6b18f2660b88eee008a8a12</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
         <is>
           <t>DRI</t>
         </is>
       </c>
-      <c r="BC12" s="2" t="inlineStr">
+      <c r="BC12" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="2" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="2" t="inlineStr">
+      <c r="BG12" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
-      <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3042,7 +3126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3482,13 +3566,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -3537,7 +3625,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f4f6d76f5b6446f58e46358acf0feae7</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>8bc9982dd4bcabf20077b66c</t>
@@ -3558,7 +3650,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -3596,8 +3692,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3846,13 +3950,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3901,7 +4009,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>cd9c53d5115c4c88a06a89280bfe5985</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>bdbc7addd11317b5a78aec33</t>
@@ -3922,7 +4034,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -3968,8 +4084,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4020,13 +4144,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4075,7 +4203,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>682734557f1646e793237149954e377d</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>dc063b21e36a663b69ad8c44</t>
@@ -4096,7 +4228,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -4142,185 +4278,19 @@
       <c r="BH5" s="2" t="inlineStr"/>
       <c r="BI5" s="2" t="inlineStr"/>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Darden Restaurants, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>DRI Q3 Deep Dive: Margin Pressures and Consumer Trends Shape Restaurant Performance</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.935</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPdmhZLVF0MThrUng3ZVdlSUU3Zk8yMERjTDF5N3h3cXREQ1p6UHdRNlpoWm0tRWFLdFhud2dFMW15dEgwYVN0aTNzQjNsZUZKR2pUT3pGczBMWHA0WERvQnh4X0Z6UGZaV1huSFpJTUdUYUdINmtPNEt5N0VKZ19qVjFUVG9CSjI2YThMMkptcWluQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>488c2fb90c1b2e6f9e17a0c6</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>a6b18f2660b88eee008a8a12</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL6"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-25.xlsx
+++ b/news_daily/2026-09-25.xlsx
@@ -1866,28 +1866,32 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1927,7 +1931,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1936,7 +1940,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>fed4b4da3b9e42f6a427acc2d89ad92c</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>ac7a8f90c724cebdda7c0d31</t>
@@ -1957,7 +1965,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1993,10 +2005,22 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2424,28 +2448,32 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2485,7 +2513,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -2494,7 +2522,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>609c7e0e61e0480a8457a664b219c9f6</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>5cf5494211d8ed3c0e855a07</t>
@@ -2515,7 +2547,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -2551,10 +2587,22 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2982,28 +3030,32 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3043,7 +3095,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -3052,7 +3104,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>84a9d64c78514f2e998a6599b3536d0f</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>14c244ee28438798ebc7d4c4</t>
@@ -3073,7 +3129,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -3109,10 +3169,22 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL13"/>
